--- a/docs/package/05_Delivery/Upload_Templates/Policies_Upload_Template.xlsx
+++ b/docs/package/05_Delivery/Upload_Templates/Policies_Upload_Template.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="119">
   <si>
     <t xml:space="preserve">Policy Number</t>
   </si>
@@ -171,24 +171,27 @@
     <t xml:space="preserve">Other accepted headers</t>
   </si>
   <si>
+    <t xml:space="preserve">Conditional: Existing policies (go-live)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Insurer policy number; for new business a BrokerVerse number is given when empty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">policyNumber, policy no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conditional: Insured Name, First Name or Company Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Full name of the insured</t>
+  </si>
+  <si>
+    <t xml:space="preserve">insuredName, client name, name</t>
+  </si>
+  <si>
     <t xml:space="preserve">No</t>
   </si>
   <si>
-    <t xml:space="preserve">Insurer policy number; a new BrokerVerse number is given when empty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">policyNumber, policy no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Conditional: Insured Name, First Name or Company Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Full name of the insured</t>
-  </si>
-  <si>
-    <t xml:space="preserve">insuredName, client name, name</t>
-  </si>
-  <si>
     <t xml:space="preserve">Text</t>
   </si>
   <si>
@@ -231,18 +234,21 @@
     <t xml:space="preserve">insuranceCompanyName, insurer</t>
   </si>
   <si>
+    <t xml:space="preserve">Date YYYY-MM-DD; for new business today when empty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">inception, effective date, start date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Date YYYY-MM-DD; for new business inception plus the default term when empty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">expiry, end date</t>
+  </si>
+  <si>
     <t xml:space="preserve">Date YYYY-MM-DD; today when empty</t>
   </si>
   <si>
-    <t xml:space="preserve">inception, effective date, start date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Date YYYY-MM-DD; inception plus the default term when empty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">expiry, end date</t>
-  </si>
-  <si>
     <t xml:space="preserve">issuedDate, issued date</t>
   </si>
   <si>
@@ -321,7 +327,7 @@
     <t xml:space="preserve">Required columns</t>
   </si>
   <si>
-    <t xml:space="preserve">Gross Premium (dark red headers on the Data sheet). Conditional: Insured Name (Insured Name, First Name or Company Name). Other columns may be left empty or removed.</t>
+    <t xml:space="preserve">Gross Premium (dark red headers on the Data sheet). Conditional: Policy Number (Existing policies (go-live)); Insured Name (Insured Name, First Name or Company Name); Insurance Company (Existing policies (go-live)); Inception Date (Existing policies (go-live)); Expiry Date (Existing policies (go-live)). Other columns may be left empty or removed.</t>
   </si>
   <si>
     <t xml:space="preserve">Header row</t>
@@ -371,9 +377,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -400,8 +406,42 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF0B2A4A"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF5F6B76"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -429,6 +469,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF4CC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -460,9 +518,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -483,6 +541,13 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -738,16 +803,16 @@
         <v>2</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E4" s="0" t="s">
         <v>19</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5">
@@ -755,16 +820,16 @@
         <v>3</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E5" s="0" t="s">
         <v>20</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6">
@@ -772,13 +837,13 @@
         <v>4</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7">
@@ -786,16 +851,16 @@
         <v>5</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E7" s="0" t="s">
         <v>21</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8">
@@ -803,16 +868,16 @@
         <v>6</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E8" s="0" t="s">
         <v>22</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="9">
@@ -820,19 +885,19 @@
         <v>7</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E9" s="0" t="s">
         <v>23</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="10">
@@ -843,13 +908,13 @@
         <v>52</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E10" s="0" t="s">
         <v>24</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11">
@@ -860,13 +925,13 @@
         <v>52</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E11" s="0" t="s">
         <v>25</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="12">
@@ -877,13 +942,13 @@
         <v>52</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E12" s="0" t="s">
         <v>26</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="13">
@@ -891,16 +956,16 @@
         <v>11</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="E13" s="0" t="s">
         <v>27</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="14">
@@ -908,16 +973,16 @@
         <v>12</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E14" s="0" t="s">
         <v>28</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15">
@@ -925,16 +990,16 @@
         <v>13</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E15" s="0" t="s">
         <v>29</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -942,16 +1007,16 @@
         <v>14</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E16" s="0" t="s">
         <v>30</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="17">
@@ -959,16 +1024,16 @@
         <v>15</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E17" s="0" t="s">
         <v>31</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="18">
@@ -976,19 +1041,19 @@
         <v>16</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E18" s="0" t="s">
         <v>32</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -1007,116 +1072,116 @@
   <sheetData>
     <row r="1" spans="1:2" ht="20" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="4" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="4" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="0" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
   </sheetData>

--- a/docs/package/05_Delivery/Upload_Templates/Policies_Upload_Template.xlsx
+++ b/docs/package/05_Delivery/Upload_Templates/Policies_Upload_Template.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="117">
   <si>
     <t xml:space="preserve">Policy Number</t>
   </si>
@@ -306,12 +306,6 @@
     <t xml:space="preserve">Operations &gt; Policy &gt; Bulk Upload</t>
   </si>
   <si>
-    <t xml:space="preserve">API route</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POST /api/policies/bulk-upload (multipart field "file"; mode=go-live for in-force policies of the old system)</t>
-  </si>
-  <si>
     <t xml:space="preserve">File types</t>
   </si>
   <si>
@@ -321,7 +315,7 @@
     <t xml:space="preserve">Row limit</t>
   </si>
   <si>
-    <t xml:space="preserve">Up to 20,000 data rows per file (IMPORT_MAX_ROWS) and 10 MB (IMPORT_MAX_MB).</t>
+    <t xml:space="preserve">Up to 20,000 data rows per file and 10 MB.</t>
   </si>
   <si>
     <t xml:space="preserve">Required columns</t>
@@ -366,10 +360,10 @@
     <t xml:space="preserve">Each row creates a new client, even if the same client appears on several rows. Co-insured policies (several insurers) cannot be uploaded; enter them on the screen.</t>
   </si>
   <si>
-    <t xml:space="preserve">Source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generated by backend/scripts/build-upload-templates.js from the column list the importer itself uses. Do not rename the headers.</t>
+    <t xml:space="preserve">Headers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The headers are the ones the import reads. Do not rename them.</t>
   </si>
 </sst>
 </file>
@@ -1063,7 +1057,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -1159,29 +1153,21 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="0" t="s">
+      <c r="B12" s="4" t="s">
         <v>113</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="4" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="0" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="14">
       <c r="B14" s="4" t="s">
         <v>116</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="0" t="s">
-        <v>117</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>118</v>
       </c>
     </row>
   </sheetData>

--- a/docs/package/05_Delivery/Upload_Templates/Policies_Upload_Template.xlsx
+++ b/docs/package/05_Delivery/Upload_Templates/Policies_Upload_Template.xlsx
@@ -303,7 +303,7 @@
     <t xml:space="preserve">Upload on</t>
   </si>
   <si>
-    <t xml:space="preserve">Operations &gt; Policy &gt; Bulk Upload</t>
+    <t xml:space="preserve">Policy Servicing &gt; Policy &gt; Bulk Upload</t>
   </si>
   <si>
     <t xml:space="preserve">File types</t>
